--- a/InputData/trans/AVOP/Avg Veh Ownership Period.xlsx
+++ b/InputData/trans/AVOP/Avg Veh Ownership Period.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\AVOP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\trans\AVOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A96E49C-1C69-4387-8BF5-89D448098612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79C522DA-3D71-43EA-A7AA-F8D27B3B86D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32340" yWindow="1425" windowWidth="23010" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="19188" windowHeight="11208" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,11 @@
     <definedName name="ti_tbl_50">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,6 +39,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -43,17 +48,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>AVOP Average Vehicle Ownership Period</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
   <si>
     <t>passenger LDVs</t>
   </si>
   <si>
-    <t>Sources:</t>
+    <t>Mint</t>
+  </si>
+  <si>
+    <t>Car owners are now selling off their vehicles earlier than usual: Report</t>
+  </si>
+  <si>
+    <t>https:https://www.livemint.com/news/india/car-owners-are-now-selling-off-their-vehicles-earlier-than-usual-report-11663849611009.html//theicct.org/wp-content/uploads/2022/10/ev-cost-benefits-2035-oct22.pdf</t>
+  </si>
+  <si>
+    <t>freight LDVs</t>
+  </si>
+  <si>
+    <t>ICRA Limited</t>
+  </si>
+  <si>
+    <t>Indian Commercial Vehicle Industry: Replacement demand emerging as a key driver for CV sales</t>
+  </si>
+  <si>
+    <t>https://theicct.org/wp-content/uploads/2022/01/cost-ev-vans-pickups-us-2040-jan22.pdf</t>
+  </si>
+  <si>
+    <t>p.4</t>
+  </si>
+  <si>
+    <t>passenger HDVs</t>
+  </si>
+  <si>
+    <t>NITI Aayog</t>
+  </si>
+  <si>
+    <t>LNG as a transportation fuel in medium &amp; heavy commercial vehicle segment</t>
+  </si>
+  <si>
+    <t>https://www.niti.gov.in/sites/default/files/2024-02/LNG%20in%20M%26HCV%20segment_07022024_updated_0.pdf</t>
+  </si>
+  <si>
+    <t>p.42</t>
   </si>
   <si>
     <t>freight HDVs</t>
   </si>
   <si>
+    <t>The Economic Times</t>
+  </si>
+  <si>
+    <t>Commercial vehicle makers count on pent-up demand, aging fleet to drive recovery</t>
+  </si>
+  <si>
+    <t>https://economictimes.indiatimes.com/industry/auto/lcv-hcv/commercial-vehicle-makers-count-on-pent-up-demand-ageing-fleet-to-drive-recovery/articleshow/89624189.cms?from=mdr</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>For rail, ships, and aircraft, we use the same data as for Average Vehicle Loading, i.e. we assume that a single owner</t>
+  </si>
+  <si>
+    <t>maintains ownership over the lifetime of the asset.</t>
+  </si>
+  <si>
+    <t>For motobikes, we use the value for passenger LDVs.</t>
+  </si>
+  <si>
+    <t>Vehicle Ownership Period (years)</t>
+  </si>
+  <si>
+    <t>passenger</t>
+  </si>
+  <si>
+    <t>freight</t>
+  </si>
+  <si>
     <t>LDVs</t>
   </si>
   <si>
@@ -70,78 +147,6 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>AVOP Average Vehicle Ownership Period</t>
-  </si>
-  <si>
-    <t>passenger</t>
-  </si>
-  <si>
-    <t>freight</t>
-  </si>
-  <si>
-    <t>Vehicle Ownership Period (years)</t>
-  </si>
-  <si>
-    <t>freight LDVs</t>
-  </si>
-  <si>
-    <t>https://theicct.org/wp-content/uploads/2022/01/cost-ev-vans-pickups-us-2040-jan22.pdf</t>
-  </si>
-  <si>
-    <t>https://theicct.org/wp-content/uploads/2023/04/tco-alt-powertrain-long-haul-trucks-us-apr23.pdf</t>
-  </si>
-  <si>
-    <t>https://theicct.org/wp-content/uploads/2022/10/ev-cost-benefits-2035-oct22.pdf</t>
-  </si>
-  <si>
-    <t>passenger HDVs</t>
-  </si>
-  <si>
-    <t>https://www.transitwiki.org/TransitWiki/images/6/64/Useful_Life_of_Buses.pdf</t>
-  </si>
-  <si>
-    <t>International Council on Clean Transportation</t>
-  </si>
-  <si>
-    <t>Assessment of Light-Duty Electric Vehicle Costs and Consumer Benefits in the United States in the 2022-2035 Time Frame</t>
-  </si>
-  <si>
-    <t>p.20</t>
-  </si>
-  <si>
-    <t>Cost of electric commercial vans and pickup trucks in the United States through 2040</t>
-  </si>
-  <si>
-    <t>p.4</t>
-  </si>
-  <si>
-    <t>Federal Transit Administration</t>
-  </si>
-  <si>
-    <t>Useful Life of Transit Buses and Vans</t>
-  </si>
-  <si>
-    <t>p.iv</t>
-  </si>
-  <si>
-    <t>p.I</t>
-  </si>
-  <si>
-    <t>Total Cost of Ownership of Alternative Powertrain Technologies for Class 8 Long-Haul Trucks in the United States</t>
-  </si>
-  <si>
-    <t>For rail, ships, and aircraft, we use the same data as for Average Vehicle Loading, i.e. we assume that a single owner</t>
-  </si>
-  <si>
-    <t>maintains ownership over the lifetime of the asset.</t>
-  </si>
-  <si>
-    <t>For motobikes, we use the value for passenger LDVs.</t>
   </si>
 </sst>
 </file>
@@ -151,9 +156,9 @@
   <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="###0.00_)"/>
-    <numFmt numFmtId="167" formatCode="#,##0_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="###0.00_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0_)"/>
   </numFmts>
   <fonts count="41">
     <font>
@@ -798,19 +803,19 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="5">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="5">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="5">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -953,7 +958,7 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="5">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyNumberFormat="0">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" applyNumberFormat="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
@@ -1014,7 +1019,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1560,17 +1565,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" customWidth="1"/>
-    <col min="2" max="2" width="85.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" customWidth="1"/>
+    <col min="2" max="2" width="85.109375" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1578,12 +1583,12 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -1594,135 +1599,125 @@
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="2">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="B18" s="2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="B8" t="s">
+    <row r="25" spans="1:2">
+      <c r="B25" s="2">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="2">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="B19" s="2">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="B21" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="B24" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="B25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="B26" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="B27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="B28" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{C01E200A-EF46-4272-B219-5D39A9156EE6}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{44931F0D-947F-4872-BF28-724517460147}"/>
-    <hyperlink ref="B21" r:id="rId3" xr:uid="{5E8C808B-3B4F-4266-85AD-76C5D16CD407}"/>
-    <hyperlink ref="B28" r:id="rId4" xr:uid="{2082B63E-16D8-42AA-97EA-01C784A3950F}"/>
+    <hyperlink ref="B7" r:id="rId1" display="https://theicct.org/wp-content/uploads/2022/10/ev-cost-benefits-2035-oct22.pdf" xr:uid="{C01E200A-EF46-4272-B219-5D39A9156EE6}"/>
+    <hyperlink ref="B13" r:id="rId2" xr:uid="{44931F0D-947F-4872-BF28-724517460147}"/>
+    <hyperlink ref="B20" r:id="rId3" xr:uid="{5E8C808B-3B4F-4266-85AD-76C5D16CD407}"/>
+    <hyperlink ref="B27" r:id="rId4" xr:uid="{2082B63E-16D8-42AA-97EA-01C784A3950F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
@@ -1735,22 +1730,22 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="60">
+    <row r="1" spans="1:37" ht="43.2">
       <c r="A1" s="9" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5"/>
       <c r="E1" s="1"/>
@@ -1789,13 +1784,13 @@
     </row>
     <row r="2" spans="1:37">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B2" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="6">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -1834,13 +1829,13 @@
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B3" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="6">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -1879,13 +1874,13 @@
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B4" s="7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -1924,13 +1919,13 @@
     </row>
     <row r="5" spans="1:37">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="6">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -1969,10 +1964,10 @@
     </row>
     <row r="6" spans="1:37">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B6" s="6">
-        <v>33</v>
+        <v>9.3333333333333339</v>
       </c>
       <c r="C6" s="6">
         <v>33</v>
@@ -2014,15 +2009,15 @@
     </row>
     <row r="7" spans="1:37">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B7" s="10">
         <f>B2</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="10">
         <f>C2</f>
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -2062,4 +2057,204 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF5FF8BB-E2DE-4D38-9C92-2286C01B3B41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{726B163A-4B49-455A-AA78-20C3B84BDAE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A069501-9804-42CD-95AE-AFC34CAE736F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>
+</clbl:labelList>
 </file>